--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1233613-3793-CM25</t>
+          <t>3638-84-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>28927.71</v>
+        <v>7206.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1233613-3835-CM25</t>
+          <t>1233613-3793-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26852.35</v>
+        <v>28927.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1233613-3836-CM25</t>
+          <t>1233613-3835-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6518.23</v>
+        <v>26852.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1233613-3837-CM25</t>
+          <t>1233613-3836-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12214.93</v>
+        <v>6518.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1237328-698-CM25</t>
+          <t>1233613-3837-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8659.559999999999</v>
+        <v>12214.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1233613-3869-CM25</t>
+          <t>1237328-698-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3635.87</v>
+        <v>8659.559999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1233613-3891-CM25</t>
+          <t>1233613-3869-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.359.312-6</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>19994.62</v>
+        <v>3635.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1233613-6817-CM25</t>
+          <t>1233613-3891-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t xml:space="preserve">AURA XD SPA </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.359.312-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8119.25</v>
+        <v>19994.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1233613-6818-CM25</t>
+          <t>1233613-6817-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28417.38</v>
+        <v>8119.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1233613-6847-CM25</t>
+          <t>1233613-6818-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8300.25</v>
+        <v>28417.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5394-12-CM26</t>
+          <t>1233613-6847-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>22595.53</v>
+        <v>8300.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1109692-9-CM26</t>
+          <t>5394-12-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>648.55</v>
+        <v>22595.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1237328-16-CM26</t>
+          <t>1109692-9-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7934.44</v>
+        <v>648.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4589-77-CM26</t>
+          <t>1237328-16-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13048.35</v>
+        <v>7934.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2663-55-CM26</t>
+          <t>4589-77-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4986.04</v>
+        <v>13048.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2663-65-CM26</t>
+          <t>2663-55-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10746.18</v>
+        <v>4986.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1237328-44-CM26</t>
+          <t>2663-65-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,32 +1530,28 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>95038.72</v>
+        <v>10746.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3638-88-CM26</t>
+          <t>1237328-44-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,28 +1591,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17255</v>
+        <v>95038.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3866-37-CM26</t>
+          <t>3638-88-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2200.93</v>
+        <v>17255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1109692-65-CM26</t>
+          <t>3866-37-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,22 +1692,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>14464.45</v>
+        <v>2200.93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3542-123-CM26</t>
+          <t>1109692-65-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>136.73</v>
+        <v>14464.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1109692-132-CM26</t>
+          <t>3542-123-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>522.41</v>
+        <v>136.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1609-123-CM26</t>
+          <t>1109692-132-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9140.629999999999</v>
+        <v>522.41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1609-122-CM26</t>
+          <t>1609-123-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>963.9</v>
+        <v>9140.629999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1609-121-CM26</t>
+          <t>1609-122-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3519.81</v>
+        <v>963.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1609-88-CM26</t>
+          <t>1609-121-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4885.19</v>
+        <v>3519.81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1609-89-CM26</t>
+          <t>1609-88-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1242.36</v>
+        <v>4885.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1237328-264-CM26</t>
+          <t>1609-89-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,32 +2205,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>91668.39999999999</v>
+        <v>1242.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1109692-181-CM26</t>
+          <t>1237328-264-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2240,12 +2236,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2255,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2270,28 +2266,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1968.12</v>
+        <v>91668.39999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1233613-1280-CM26</t>
+          <t>1109692-181-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1234.02</v>
+        <v>1968.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1233613-1281-CM26</t>
+          <t>1233613-1280-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>25773.02</v>
+        <v>1234.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1233613-1282-CM26</t>
+          <t>1233613-1281-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1511.28</v>
+        <v>25773.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5394-367-CM26</t>
+          <t>1233613-1282-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2529,13 +2529,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7234.72</v>
+        <v>1511.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5394-370-CM26</t>
+          <t>5394-367-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2545,17 +2545,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2380</v>
+        <v>7234.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5394-369-CM26</t>
+          <t>5394-370-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2272.9</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1237328-381-CM26</t>
+          <t>5394-369-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10979.89</v>
+        <v>2272.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5394-391-CM26</t>
+          <t>1237328-381-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2733,22 +2733,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2773,13 +2773,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1234.02</v>
+        <v>10979.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5338-379-CM26</t>
+          <t>5394-391-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2468.04</v>
+        <v>1234.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5338-380-CM26</t>
+          <t>5338-379-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>469.55</v>
+        <v>2468.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1233613-1327-CM26</t>
+          <t>5338-380-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2956,13 +2956,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>16207.44</v>
+        <v>469.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1233613-1328-CM26</t>
+          <t>1233613-1327-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8643.969999999999</v>
+        <v>16207.44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1233613-1329-CM26</t>
+          <t>1233613-1328-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1620.74</v>
+        <v>8643.969999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2348-313-CM26</t>
+          <t>1233613-1329-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3124,32 +3124,28 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>87167.21000000001</v>
+        <v>1620.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3542-206-CM26</t>
+          <t>2348-313-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3164,22 +3160,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3189,28 +3185,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>23779.82</v>
+        <v>87167.21000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4589-342-CM26</t>
+          <t>3542-206-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3265,13 +3265,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2909.91</v>
+        <v>23779.82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1233613-1287-CM26</t>
+          <t>4589-342-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3326,6 +3326,67 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
+        <v>2909.91</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1233613-1287-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.980.960-2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Magallanes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
         <v>1070.98</v>
       </c>
     </row>
